--- a/Miscellaneous/Rekindle the Green Database Schema.xlsx
+++ b/Miscellaneous/Rekindle the Green Database Schema.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a7b2e265512bf4b7/Documents/college/WPL/Rekindle-the-Green/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\Rekindle-the-Green\Miscellaneous\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="8_{8627C4DC-4674-4145-A004-EDBF6CB81C42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55A5048B-951D-432E-A0CF-0B9FB6429378}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88AF7D87-87BB-4E47-BA0E-09297EDA4882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="528" yWindow="792" windowWidth="19404" windowHeight="10740" xr2:uid="{E049C550-504B-4D65-B260-6756B5056B05}"/>
+    <workbookView xWindow="1224" yWindow="1488" windowWidth="19404" windowHeight="10740" xr2:uid="{E049C550-504B-4D65-B260-6756B5056B05}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
   <si>
     <t>person_id</t>
   </si>
@@ -74,14 +74,20 @@
     <t>drive</t>
   </si>
   <si>
-    <t>register</t>
+    <t>admins</t>
+  </si>
+  <si>
+    <t>admin_id</t>
+  </si>
+  <si>
+    <t>password</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -106,7 +112,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -129,14 +135,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -152,10 +170,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -475,15 +489,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C08ADEC-EA92-46FB-9835-788211499F2B}">
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -499,13 +513,16 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="F2" s="3" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
@@ -522,17 +539,29 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
